--- a/metadata_example.xlsx
+++ b/metadata_example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefanhallermann/Library/CloudStorage/Dropbox/tmp/iGluSnFr/test01/in/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefanhallermann/Library/CloudStorage/Dropbox/tmp/Py/iGluSnFr/test03SH/in/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E887B966-5821-0B4E-8AD8-54FEF78379BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4AE2A4-6751-D948-B807-DA8CEE6C25A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="500" windowWidth="28040" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata_SH01" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>experimentName</t>
   </si>
@@ -113,6 +113,33 @@
   </si>
   <si>
     <t>202511xx_2</t>
+  </si>
+  <si>
+    <t>Train_Bsl_Start</t>
+  </si>
+  <si>
+    <t>Train_Bsl_End</t>
+  </si>
+  <si>
+    <t>Train_Peak_Start</t>
+  </si>
+  <si>
+    <t>Train_Peak_End</t>
+  </si>
+  <si>
+    <t>Recalc_CSV</t>
+  </si>
+  <si>
+    <t>Exclude_ROI_when_PrA&gt;xx</t>
+  </si>
+  <si>
+    <t>Exclude_ROI_when_#excludedStim&gt;xx</t>
+  </si>
+  <si>
+    <t>Exclude_stim_when_baseline&gt;xx%_of_ min_bsl_per_trace</t>
+  </si>
+  <si>
+    <t>Exclude_ROI_when_trainBC&lt;xx-fold</t>
   </si>
 </sst>
 </file>
@@ -442,7 +469,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -555,6 +582,119 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="slantDashDot">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="slantDashDot">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="slantDashDot">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="slantDashDot">
+        <color auto="1"/>
+      </right>
+      <top style="slantDashDot">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="slantDashDot">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="slantDashDot">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -602,8 +742,19 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -979,246 +1130,335 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z3"/>
+  <dimension ref="A1:AI3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="10.83203125" style="7"/>
+    <col min="11" max="11" width="10.83203125" style="10"/>
+    <col min="12" max="12" width="10.83203125" style="11"/>
+    <col min="20" max="20" width="10.83203125" style="4"/>
+    <col min="23" max="23" width="10.83203125" style="5"/>
+    <col min="27" max="27" width="10.83203125" style="11"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>21</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>24</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>25</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>26</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>27</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>28</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>29</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="X1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB1" t="s">
         <v>8</v>
       </c>
-      <c r="T1" t="s">
+      <c r="AC1" t="s">
         <v>9</v>
       </c>
-      <c r="U1" t="s">
+      <c r="AD1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" t="s">
+      <c r="AE1" t="s">
         <v>10</v>
       </c>
-      <c r="W1" t="s">
+      <c r="AF1" t="s">
         <v>11</v>
       </c>
-      <c r="X1" t="s">
+      <c r="AG1" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AH1" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AI1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>15</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="7">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>500</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>1000</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>10</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>250</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>1000</v>
-      </c>
-      <c r="G2">
-        <v>250</v>
       </c>
       <c r="H2">
         <v>250</v>
       </c>
       <c r="I2">
+        <v>250</v>
+      </c>
+      <c r="J2">
         <v>10000</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="10">
         <v>13000</v>
       </c>
-      <c r="K2">
+      <c r="L2" s="11">
         <v>10000</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>10500</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>11000</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>11500</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>10000</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>10500</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>11000</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>11500</v>
       </c>
-      <c r="S2">
+      <c r="T2" s="4">
+        <v>10250</v>
+      </c>
+      <c r="U2">
+        <v>10600</v>
+      </c>
+      <c r="V2">
+        <v>11250</v>
+      </c>
+      <c r="W2" s="5">
+        <v>11750</v>
+      </c>
+      <c r="X2">
+        <v>3</v>
+      </c>
+      <c r="Y2">
+        <v>0.9</v>
+      </c>
+      <c r="Z2">
+        <v>3</v>
+      </c>
+      <c r="AA2" s="11">
         <v>10</v>
       </c>
-      <c r="T2">
+      <c r="AB2">
+        <v>10</v>
+      </c>
+      <c r="AC2">
         <v>4</v>
       </c>
-      <c r="U2">
+      <c r="AD2">
         <v>50</v>
       </c>
-      <c r="V2">
+      <c r="AE2">
         <v>1.25</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AF2" t="s">
         <v>16</v>
       </c>
-      <c r="X2" t="s">
+      <c r="AG2" t="s">
         <v>17</v>
       </c>
-      <c r="Y2">
+      <c r="AH2">
         <v>30</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AI2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>30</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="7">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>500</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1000</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>10</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>250</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>1000</v>
-      </c>
-      <c r="G3">
-        <v>250</v>
       </c>
       <c r="H3">
         <v>250</v>
       </c>
       <c r="I3">
+        <v>250</v>
+      </c>
+      <c r="J3">
         <v>10000</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="10">
         <v>13000</v>
       </c>
-      <c r="K3">
+      <c r="L3" s="11">
         <v>10000</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>10500</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>11000</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>11500</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>10000</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>10500</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>11000</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>11500</v>
       </c>
-      <c r="S3">
+      <c r="T3" s="4">
+        <v>10250</v>
+      </c>
+      <c r="U3">
+        <v>10600</v>
+      </c>
+      <c r="V3">
+        <v>11250</v>
+      </c>
+      <c r="W3" s="5">
+        <v>11750</v>
+      </c>
+      <c r="X3">
+        <v>3</v>
+      </c>
+      <c r="Y3">
+        <v>0.9</v>
+      </c>
+      <c r="Z3">
+        <v>3</v>
+      </c>
+      <c r="AA3" s="11">
         <v>10</v>
       </c>
-      <c r="T3">
+      <c r="AB3">
+        <v>10</v>
+      </c>
+      <c r="AC3">
         <v>4</v>
       </c>
-      <c r="U3">
+      <c r="AD3">
         <v>50</v>
       </c>
-      <c r="V3">
+      <c r="AE3">
         <v>1.25</v>
       </c>
-      <c r="W3" t="s">
+      <c r="AF3" t="s">
         <v>16</v>
       </c>
-      <c r="X3" t="s">
+      <c r="AG3" t="s">
         <v>17</v>
       </c>
-      <c r="Y3">
+      <c r="AH3">
         <v>30</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AI3" t="s">
         <v>18</v>
       </c>
     </row>
